--- a/exports/trend_1d/HINDUNILVR_full_report.xlsx
+++ b/exports/trend_1d/HINDUNILVR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>869.5</v>
+        <v>849.4</v>
       </c>
       <c r="I2" t="n">
         <v>864.7362847740187</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.81</v>
+        <v>-6.03</v>
       </c>
       <c r="L2" t="n">
-        <v>4.75</v>
+        <v>6.87</v>
       </c>
       <c r="M2" t="n">
         <v>0.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>9.59</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42104</v>
+        <v>42107</v>
       </c>
       <c r="H3" t="n">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="I3" t="n">
         <v>918.1843169894071</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.84</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>8.06</v>
+        <v>9.82</v>
       </c>
       <c r="M3" t="n">
         <v>0.79</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.06</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>896</v>
+        <v>856.4</v>
       </c>
       <c r="I4" t="n">
         <v>859.2166110727828</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.76</v>
+        <v>-8.01</v>
       </c>
       <c r="L4" t="n">
-        <v>4.59</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>0.66</v>
       </c>
       <c r="N4" t="n">
-        <v>2.58</v>
+        <v>4.42</v>
       </c>
       <c r="O4" t="n">
         <v>1.64</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.12</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42178</v>
+        <v>42179</v>
       </c>
       <c r="H5" t="n">
-        <v>859</v>
+        <v>879.4</v>
       </c>
       <c r="I5" t="n">
         <v>860.0198116675251</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3</v>
+        <v>-2.69</v>
       </c>
       <c r="L5" t="n">
         <v>5.6</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.27</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H6" t="n">
-        <v>871.2</v>
+        <v>849.8</v>
       </c>
       <c r="I6" t="n">
         <v>856.4960792516703</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.93</v>
+        <v>-3.37</v>
       </c>
       <c r="L6" t="n">
-        <v>3.14</v>
+        <v>4.12</v>
       </c>
       <c r="M6" t="n">
         <v>1.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
         <v>2.37</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42349</v>
+        <v>42352</v>
       </c>
       <c r="H7" t="n">
-        <v>806.4</v>
+        <v>823</v>
       </c>
       <c r="I7" t="n">
         <v>820.5411032073231</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K7" t="n">
-        <v>5.11</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>4.1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42376</v>
+        <v>42377</v>
       </c>
       <c r="H8" t="n">
-        <v>804.6</v>
+        <v>794.4</v>
       </c>
       <c r="I8" t="n">
         <v>801.7533878794986</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.24</v>
+        <v>-3.48</v>
       </c>
       <c r="L8" t="n">
-        <v>3.05</v>
+        <v>3.73</v>
       </c>
       <c r="M8" t="n">
         <v>1.8</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.24</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42404</v>
+        <v>42405</v>
       </c>
       <c r="H9" t="n">
-        <v>818.9</v>
+        <v>828.8</v>
       </c>
       <c r="I9" t="n">
         <v>819.0443986022025</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.08</v>
+        <v>-4.33</v>
       </c>
       <c r="L9" t="n">
-        <v>3.52</v>
+        <v>5.64</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.15</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42496</v>
+        <v>42499</v>
       </c>
       <c r="H10" t="n">
-        <v>837.1</v>
+        <v>829.4</v>
       </c>
       <c r="I10" t="n">
         <v>832.9381321045379</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>6.53</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.32</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42523</v>
+        <v>42524</v>
       </c>
       <c r="H11" t="n">
-        <v>851.6</v>
+        <v>867.9</v>
       </c>
       <c r="I11" t="n">
         <v>853.1821757488448</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.68</v>
+        <v>-4.64</v>
       </c>
       <c r="L11" t="n">
-        <v>3.36</v>
+        <v>5.02</v>
       </c>
       <c r="M11" t="n">
         <v>0.6</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.31</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42636</v>
+        <v>42639</v>
       </c>
       <c r="H12" t="n">
-        <v>893.2</v>
+        <v>875.6</v>
       </c>
       <c r="I12" t="n">
         <v>878.3225458286289</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K12" t="n">
-        <v>2.92</v>
+        <v>0.89</v>
       </c>
       <c r="L12" t="n">
         <v>4.26</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.54</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H13" t="n">
-        <v>814.7</v>
+        <v>825.4</v>
       </c>
       <c r="I13" t="n">
         <v>818.2184291665185</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K13" t="n">
-        <v>6.96</v>
+        <v>5.73</v>
       </c>
       <c r="L13" t="n">
         <v>2.38</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.03</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H14" t="n">
-        <v>1194.1</v>
+        <v>1182.9</v>
       </c>
       <c r="I14" t="n">
         <v>1187.852028929695</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K14" t="n">
-        <v>44.67</v>
+        <v>43.31</v>
       </c>
       <c r="L14" t="n">
         <v>2.27</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>6.33</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H15" t="n">
-        <v>1224.8</v>
+        <v>1256.8</v>
       </c>
       <c r="I15" t="n">
         <v>1237.672045642715</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.54</v>
+        <v>-6.25</v>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>6.76</v>
       </c>
       <c r="M15" t="n">
         <v>0.84</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>2.61</v>
       </c>
       <c r="O15" t="n">
         <v>-0.9399999999999999</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="H16" t="n">
-        <v>1300</v>
+        <v>1287.6</v>
       </c>
       <c r="I16" t="n">
         <v>1299.244412463788</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K16" t="n">
-        <v>3.44</v>
+        <v>2.45</v>
       </c>
       <c r="L16" t="n">
         <v>4.29</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>7.22</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H17" t="n">
-        <v>1331.5</v>
+        <v>1355.8</v>
       </c>
       <c r="I17" t="n">
         <v>1334.030753340832</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.41</v>
+        <v>-5.3</v>
       </c>
       <c r="L17" t="n">
-        <v>3.95</v>
+        <v>5.42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
         <v>-0.95</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.7</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43298</v>
+        <v>43299</v>
       </c>
       <c r="H18" t="n">
-        <v>1649.6</v>
+        <v>1612.4</v>
       </c>
       <c r="I18" t="n">
         <v>1638.243884084731</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K18" t="n">
-        <v>21.67</v>
+        <v>18.93</v>
       </c>
       <c r="L18" t="n">
         <v>1.43</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.68</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43328</v>
+        <v>43329</v>
       </c>
       <c r="H19" t="n">
-        <v>1704.2</v>
+        <v>1750.7</v>
       </c>
       <c r="I19" t="n">
         <v>1736.004992652008</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.69</v>
+        <v>-8.58</v>
       </c>
       <c r="L19" t="n">
-        <v>7.52</v>
+        <v>8.81</v>
       </c>
       <c r="M19" t="n">
         <v>0.79</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="O19" t="n">
         <v>-2.26</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.21</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H20" t="n">
-        <v>1666.6</v>
+        <v>1619.7</v>
       </c>
       <c r="I20" t="n">
         <v>1661.152949076162</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.8</v>
+        <v>-7.48</v>
       </c>
       <c r="L20" t="n">
-        <v>4.98</v>
+        <v>9.02</v>
       </c>
       <c r="M20" t="n">
         <v>0.19</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.86</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H21" t="n">
-        <v>1600.8</v>
+        <v>1640.7</v>
       </c>
       <c r="I21" t="n">
         <v>1625.517207125857</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K21" t="n">
-        <v>1.17</v>
+        <v>-1.3</v>
       </c>
       <c r="L21" t="n">
         <v>2.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43494</v>
+        <v>43495</v>
       </c>
       <c r="H22" t="n">
-        <v>1723.1</v>
+        <v>1700.2</v>
       </c>
       <c r="I22" t="n">
         <v>1702.959226253156</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K22" t="n">
-        <v>5.02</v>
+        <v>3.63</v>
       </c>
       <c r="L22" t="n">
         <v>2.16</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.93</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43502</v>
+        <v>43503</v>
       </c>
       <c r="H23" t="n">
-        <v>1795</v>
+        <v>1803.9</v>
       </c>
       <c r="I23" t="n">
         <v>1800.992155919349</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.58</v>
+        <v>-6.1</v>
       </c>
       <c r="L23" t="n">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="M23" t="n">
         <v>0.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.22</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43514</v>
+        <v>43515</v>
       </c>
       <c r="H24" t="n">
-        <v>1718.4</v>
+        <v>1704.8</v>
       </c>
       <c r="I24" t="n">
         <v>1709.804014166065</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.74</v>
+        <v>-5.49</v>
       </c>
       <c r="L24" t="n">
-        <v>5.65</v>
+        <v>5.9</v>
       </c>
       <c r="M24" t="n">
         <v>0.34</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.71</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43570</v>
+        <v>43571</v>
       </c>
       <c r="H25" t="n">
-        <v>1689.2</v>
+        <v>1705.3</v>
       </c>
       <c r="I25" t="n">
         <v>1704.345168684107</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K25" t="n">
-        <v>0.92</v>
+        <v>-0.03</v>
       </c>
       <c r="L25" t="n">
         <v>2.76</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.63</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43588</v>
+        <v>43591</v>
       </c>
       <c r="H26" t="n">
-        <v>1661.2</v>
+        <v>1637</v>
       </c>
       <c r="I26" t="n">
         <v>1654.561626953635</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.59</v>
+        <v>-4.01</v>
       </c>
       <c r="L26" t="n">
-        <v>3.25</v>
+        <v>4.74</v>
       </c>
       <c r="M26" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="N26" t="n">
         <v>1.94</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>5.09</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H27" t="n">
-        <v>1703.6</v>
+        <v>1738.6</v>
       </c>
       <c r="I27" t="n">
         <v>1720.2753239508</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.07</v>
+        <v>-6.21</v>
       </c>
       <c r="L27" t="n">
-        <v>4.39</v>
+        <v>6.46</v>
       </c>
       <c r="M27" t="n">
-        <v>0.59</v>
+        <v>1.34</v>
       </c>
       <c r="N27" t="n">
         <v>2.87</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6.61</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H28" t="n">
-        <v>1720.1</v>
+        <v>1707</v>
       </c>
       <c r="I28" t="n">
         <v>1712.401380188647</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.06</v>
+        <v>-1.82</v>
       </c>
       <c r="L28" t="n">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="M28" t="n">
         <v>0.7</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>4.98</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43684</v>
+        <v>43685</v>
       </c>
       <c r="H29" t="n">
-        <v>1743.3</v>
+        <v>1768.7</v>
       </c>
       <c r="I29" t="n">
         <v>1766.580430009205</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.13</v>
+        <v>-3.61</v>
       </c>
       <c r="L29" t="n">
-        <v>2.68</v>
+        <v>3.84</v>
       </c>
       <c r="M29" t="n">
         <v>0.51</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43783</v>
+        <v>43784</v>
       </c>
       <c r="H30" t="n">
-        <v>2029.5</v>
+        <v>2018.4</v>
       </c>
       <c r="I30" t="n">
         <v>2021.645438686076</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K30" t="n">
-        <v>14.75</v>
+        <v>14.12</v>
       </c>
       <c r="L30" t="n">
         <v>1.26</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.46</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43843</v>
+        <v>43844</v>
       </c>
       <c r="H31" t="n">
-        <v>1956.7</v>
+        <v>1970.4</v>
       </c>
       <c r="I31" t="n">
         <v>1961.990929370608</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K31" t="n">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="L31" t="n">
         <v>2.05</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.66</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H32" t="n">
-        <v>2147.1</v>
+        <v>2081</v>
       </c>
       <c r="I32" t="n">
         <v>2081.360944239978</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K32" t="n">
-        <v>8.970000000000001</v>
+        <v>5.61</v>
       </c>
       <c r="L32" t="n">
         <v>1.31</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>10.08</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43915</v>
+        <v>43916</v>
       </c>
       <c r="H33" t="n">
-        <v>2048.3</v>
+        <v>2153</v>
       </c>
       <c r="I33" t="n">
         <v>2114.165594310217</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>1.57</v>
+        <v>-3.46</v>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>6.05</v>
       </c>
       <c r="M33" t="n">
         <v>5.63</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>21.3</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43956</v>
+        <v>43957</v>
       </c>
       <c r="H34" t="n">
-        <v>2002.5</v>
+        <v>1971.8</v>
       </c>
       <c r="I34" t="n">
         <v>1995.373039188231</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.99</v>
+        <v>-8.42</v>
       </c>
       <c r="L34" t="n">
-        <v>7.37</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>2.96</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>17.16</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44008</v>
+        <v>44011</v>
       </c>
       <c r="H35" t="n">
-        <v>2113.1</v>
+        <v>2141.3</v>
       </c>
       <c r="I35" t="n">
         <v>2138.978911676175</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.17</v>
+        <v>-8.6</v>
       </c>
       <c r="L35" t="n">
-        <v>8.94</v>
+        <v>9.24</v>
       </c>
       <c r="M35" t="n">
         <v>4.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.95</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44056</v>
+        <v>44057</v>
       </c>
       <c r="H36" t="n">
-        <v>2156.7</v>
+        <v>2132.4</v>
       </c>
       <c r="I36" t="n">
         <v>2142.729543120028</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K36" t="n">
-        <v>0.72</v>
+        <v>-0.42</v>
       </c>
       <c r="L36" t="n">
         <v>2.66</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.08</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H37" t="n">
-        <v>2098.5</v>
+        <v>2119.5</v>
       </c>
       <c r="I37" t="n">
         <v>2115.651912573283</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K37" t="n">
-        <v>1.59</v>
+        <v>0.6</v>
       </c>
       <c r="L37" t="n">
         <v>2.19</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.86</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44137</v>
+        <v>44138</v>
       </c>
       <c r="H38" t="n">
-        <v>2032.4</v>
+        <v>2016.4</v>
       </c>
       <c r="I38" t="n">
         <v>2019.897195847686</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.11</v>
+        <v>-4.86</v>
       </c>
       <c r="L38" t="n">
-        <v>4.85</v>
+        <v>5.45</v>
       </c>
       <c r="M38" t="n">
         <v>1.03</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H39" t="n">
-        <v>2090.4</v>
+        <v>2150.2</v>
       </c>
       <c r="I39" t="n">
         <v>2150.171689425405</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.67</v>
+        <v>-6.64</v>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>7.22</v>
       </c>
       <c r="M39" t="n">
         <v>1.31</v>
       </c>
       <c r="N39" t="n">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
         <v>-0.79</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H40" t="n">
-        <v>2256.5</v>
+        <v>2220.7</v>
       </c>
       <c r="I40" t="n">
         <v>2249.809298451079</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K40" t="n">
-        <v>4.94</v>
+        <v>3.28</v>
       </c>
       <c r="L40" t="n">
         <v>4.43</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44273</v>
+        <v>44274</v>
       </c>
       <c r="H41" t="n">
-        <v>2172.9</v>
+        <v>2267.9</v>
       </c>
       <c r="I41" t="n">
         <v>2221.096064843442</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K41" t="n">
-        <v>2.15</v>
+        <v>-2.13</v>
       </c>
       <c r="L41" t="n">
-        <v>2.58</v>
+        <v>2.71</v>
       </c>
       <c r="M41" t="n">
         <v>1.24</v>
       </c>
       <c r="N41" t="n">
-        <v>1.61</v>
+        <v>4.37</v>
       </c>
       <c r="O41" t="n">
         <v>-1.59</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.76</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44308</v>
+        <v>44309</v>
       </c>
       <c r="H42" t="n">
-        <v>2304.5</v>
+        <v>2263.7</v>
       </c>
       <c r="I42" t="n">
         <v>2264.260126331629</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K42" t="n">
-        <v>1.61</v>
+        <v>-0.19</v>
       </c>
       <c r="L42" t="n">
         <v>5.22</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H43" t="n">
-        <v>2371.5</v>
+        <v>2435.5</v>
       </c>
       <c r="I43" t="n">
         <v>2398.199675579904</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.76</v>
+        <v>-7.59</v>
       </c>
       <c r="L43" t="n">
-        <v>6.12</v>
+        <v>8.19</v>
       </c>
       <c r="M43" t="n">
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
         <v>-1.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.17</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44397</v>
+        <v>44399</v>
       </c>
       <c r="H44" t="n">
-        <v>2388.4</v>
+        <v>2332.7</v>
       </c>
       <c r="I44" t="n">
         <v>2335.357061208337</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.93</v>
+        <v>-4.22</v>
       </c>
       <c r="L44" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="M44" t="n">
         <v>0.78</v>
       </c>
       <c r="N44" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="O44" t="n">
         <v>2.7</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.27</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44424</v>
+        <v>44425</v>
       </c>
       <c r="H45" t="n">
-        <v>2380.1</v>
+        <v>2436.4</v>
       </c>
       <c r="I45" t="n">
         <v>2405.805408880066</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.03</v>
+        <v>-4.45</v>
       </c>
       <c r="L45" t="n">
         <v>5.46</v>
@@ -3006,7 +3545,7 @@
         <v>0.62</v>
       </c>
       <c r="N45" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="O45" t="n">
         <v>-2.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.57</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44476</v>
+        <v>44477</v>
       </c>
       <c r="H46" t="n">
-        <v>2618.4</v>
+        <v>2589.6</v>
       </c>
       <c r="I46" t="n">
         <v>2603.531777831354</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K46" t="n">
-        <v>7.47</v>
+        <v>6.29</v>
       </c>
       <c r="L46" t="n">
         <v>2.13</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.01</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H47" t="n">
-        <v>2316.2</v>
+        <v>2355.4</v>
       </c>
       <c r="I47" t="n">
         <v>2325.348195161789</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K47" t="n">
-        <v>10.56</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>3.48</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.58</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H48" t="n">
-        <v>2324.2</v>
+        <v>2265.8</v>
       </c>
       <c r="I48" t="n">
         <v>2272.174768905015</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.32</v>
+        <v>-3.8</v>
       </c>
       <c r="L48" t="n">
-        <v>2.34</v>
+        <v>4.01</v>
       </c>
       <c r="M48" t="n">
         <v>0.74</v>
       </c>
       <c r="N48" t="n">
-        <v>2.09</v>
+        <v>2.51</v>
       </c>
       <c r="O48" t="n">
         <v>1.69</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.42</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H49" t="n">
-        <v>2038.5</v>
+        <v>2087.8</v>
       </c>
       <c r="I49" t="n">
         <v>2069.385400954854</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K49" t="n">
-        <v>10.03</v>
+        <v>7.86</v>
       </c>
       <c r="L49" t="n">
         <v>2.54</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.23</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44725</v>
+        <v>44726</v>
       </c>
       <c r="H50" t="n">
-        <v>2154.9</v>
+        <v>2129.5</v>
       </c>
       <c r="I50" t="n">
         <v>2130.161995812214</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K50" t="n">
-        <v>3.21</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
         <v>3.83</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.59</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H51" t="n">
-        <v>2209.6</v>
+        <v>2259.9</v>
       </c>
       <c r="I51" t="n">
         <v>2246.399225639129</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.76</v>
+        <v>-6.12</v>
       </c>
       <c r="L51" t="n">
-        <v>3.98</v>
+        <v>6.81</v>
       </c>
       <c r="M51" t="n">
         <v>0.62</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H52" t="n">
-        <v>2511.5</v>
+        <v>2479.9</v>
       </c>
       <c r="I52" t="n">
         <v>2489.523191968421</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K52" t="n">
-        <v>11.13</v>
+        <v>9.73</v>
       </c>
       <c r="L52" t="n">
         <v>4.35</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.3</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44825</v>
+        <v>44826</v>
       </c>
       <c r="H53" t="n">
-        <v>2573.5</v>
+        <v>2641.3</v>
       </c>
       <c r="I53" t="n">
         <v>2636.122439711039</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.77</v>
+        <v>-6.51</v>
       </c>
       <c r="L53" t="n">
-        <v>4.69</v>
+        <v>6.85</v>
       </c>
       <c r="M53" t="n">
         <v>0.75</v>
       </c>
       <c r="N53" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="O53" t="n">
         <v>-1.26</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.36</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44858</v>
+        <v>44859</v>
       </c>
       <c r="H54" t="n">
-        <v>2524</v>
+        <v>2457.5</v>
       </c>
       <c r="I54" t="n">
         <v>2493.096512430076</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.44</v>
+        <v>-6.96</v>
       </c>
       <c r="L54" t="n">
-        <v>5.6</v>
+        <v>7.16</v>
       </c>
       <c r="M54" t="n">
         <v>1.65</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.99</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44893</v>
+        <v>44894</v>
       </c>
       <c r="H55" t="n">
-        <v>2477</v>
+        <v>2583.9</v>
       </c>
       <c r="I55" t="n">
         <v>2549.429754850572</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.79</v>
+        <v>-5.14</v>
       </c>
       <c r="L55" t="n">
-        <v>3.22</v>
+        <v>5.37</v>
       </c>
       <c r="M55" t="n">
         <v>1.25</v>
       </c>
       <c r="N55" t="n">
-        <v>1.67</v>
+        <v>4.32</v>
       </c>
       <c r="O55" t="n">
         <v>-2.63</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.39</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44922</v>
+        <v>44923</v>
       </c>
       <c r="H56" t="n">
-        <v>2543.7</v>
+        <v>2534.3</v>
       </c>
       <c r="I56" t="n">
         <v>2534.848698343729</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.56</v>
+        <v>-1.92</v>
       </c>
       <c r="L56" t="n">
         <v>4.06</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.29</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44942</v>
+        <v>44943</v>
       </c>
       <c r="H57" t="n">
-        <v>2547.5</v>
+        <v>2616.6</v>
       </c>
       <c r="I57" t="n">
         <v>2610.853955764872</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.52</v>
+        <v>-3.25</v>
       </c>
       <c r="L57" t="n">
-        <v>2.7</v>
+        <v>3.54</v>
       </c>
       <c r="M57" t="n">
         <v>0.5</v>
       </c>
       <c r="N57" t="n">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="O57" t="n">
         <v>-0.37</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.57</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H58" t="n">
-        <v>2499.8</v>
+        <v>2478.8</v>
       </c>
       <c r="I58" t="n">
         <v>2486.853391378014</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.46</v>
+        <v>-5.27</v>
       </c>
       <c r="L58" t="n">
-        <v>5.15</v>
+        <v>5.42</v>
       </c>
       <c r="M58" t="n">
         <v>3.76</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>5.92</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H59" t="n">
-        <v>2482.5</v>
+        <v>2511.4</v>
       </c>
       <c r="I59" t="n">
         <v>2492.635153072735</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.15</v>
+        <v>-1.32</v>
       </c>
       <c r="L59" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="M59" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="N59" t="n">
         <v>2.6</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.99</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H60" t="n">
-        <v>2651.6</v>
+        <v>2554.3</v>
       </c>
       <c r="I60" t="n">
         <v>2579.991263937856</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K60" t="n">
-        <v>5.58</v>
+        <v>1.71</v>
       </c>
       <c r="L60" t="n">
         <v>5.52</v>
       </c>
       <c r="M60" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="N60" t="n">
-        <v>2.14</v>
+        <v>3.67</v>
       </c>
       <c r="O60" t="n">
         <v>1.16</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.02</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45209</v>
+        <v>45210</v>
       </c>
       <c r="H61" t="n">
-        <v>2468.1</v>
+        <v>2507.6</v>
       </c>
       <c r="I61" t="n">
         <v>2505.22259563428</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K61" t="n">
-        <v>3.37</v>
+        <v>1.83</v>
       </c>
       <c r="L61" t="n">
         <v>2.78</v>
@@ -3918,7 +4649,7 @@
         <v>0.99</v>
       </c>
       <c r="N61" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O61" t="n">
         <v>-3.67</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.56</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="H62" t="n">
-        <v>2528.2</v>
+        <v>2487.8</v>
       </c>
       <c r="I62" t="n">
         <v>2506.488464036823</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K62" t="n">
-        <v>0.82</v>
+        <v>-0.79</v>
       </c>
       <c r="L62" t="n">
         <v>3.94</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.3</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H63" t="n">
-        <v>2213.1</v>
+        <v>2334</v>
       </c>
       <c r="I63" t="n">
         <v>2255.783041068072</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K63" t="n">
-        <v>11.04</v>
+        <v>6.18</v>
       </c>
       <c r="L63" t="n">
         <v>2.08</v>
@@ -4032,7 +4787,7 @@
         <v>0.82</v>
       </c>
       <c r="N63" t="n">
-        <v>2.78</v>
+        <v>5.46</v>
       </c>
       <c r="O63" t="n">
         <v>-1.6</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.72</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45572</v>
+        <v>45573</v>
       </c>
       <c r="H64" t="n">
-        <v>2779.3</v>
+        <v>2765</v>
       </c>
       <c r="I64" t="n">
         <v>2767.20521690811</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K64" t="n">
-        <v>19.08</v>
+        <v>18.47</v>
       </c>
       <c r="L64" t="n">
         <v>5.06</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.86</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H65" t="n">
-        <v>2355.1</v>
+        <v>2388.9</v>
       </c>
       <c r="I65" t="n">
         <v>2385.807734087497</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K65" t="n">
-        <v>14.82</v>
+        <v>13.6</v>
       </c>
       <c r="L65" t="n">
         <v>2.38</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.66</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H66" t="n">
-        <v>2316.3</v>
+        <v>2271</v>
       </c>
       <c r="I66" t="n">
         <v>2291.853184257543</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.04</v>
+        <v>-4.94</v>
       </c>
       <c r="L66" t="n">
         <v>7.46</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="H67" t="n">
-        <v>2245.5</v>
+        <v>2305.1</v>
       </c>
       <c r="I67" t="n">
         <v>2251.49544136798</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K67" t="n">
-        <v>1.12</v>
+        <v>-1.5</v>
       </c>
       <c r="L67" t="n">
         <v>2.71</v>
@@ -4260,7 +5063,7 @@
         <v>0.85</v>
       </c>
       <c r="N67" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="O67" t="n">
         <v>-1.96</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>8.16</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45828</v>
+        <v>45831</v>
       </c>
       <c r="H68" t="n">
-        <v>2262.2</v>
+        <v>2231.6</v>
       </c>
       <c r="I68" t="n">
         <v>2246.346848497138</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.86</v>
+        <v>-3.19</v>
       </c>
       <c r="L68" t="n">
-        <v>2.75</v>
+        <v>3.88</v>
       </c>
       <c r="M68" t="n">
         <v>1.18</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>4.22</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45842</v>
+        <v>45845</v>
       </c>
       <c r="H69" t="n">
-        <v>2294.6</v>
+        <v>2364.4</v>
       </c>
       <c r="I69" t="n">
         <v>2325.86826123293</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.82</v>
+        <v>-5.95</v>
       </c>
       <c r="L69" t="n">
-        <v>2.92</v>
+        <v>6.18</v>
       </c>
       <c r="M69" t="n">
         <v>0.88</v>
       </c>
       <c r="N69" t="n">
-        <v>1.14</v>
+        <v>3.04</v>
       </c>
       <c r="O69" t="n">
         <v>-1.35</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.49</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H70" t="n">
-        <v>2523.1</v>
+        <v>2474</v>
       </c>
       <c r="I70" t="n">
         <v>2475.798059599969</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K70" t="n">
-        <v>6.71</v>
+        <v>4.64</v>
       </c>
       <c r="L70" t="n">
         <v>2.88</v>
@@ -4431,7 +5270,7 @@
         <v>0.78</v>
       </c>
       <c r="N70" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="O70" t="n">
         <v>3.04</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.18</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H71" t="n">
-        <v>2348</v>
+        <v>2384.1</v>
       </c>
       <c r="I71" t="n">
         <v>2375.803899909631</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K71" t="n">
-        <v>5.09</v>
+        <v>3.63</v>
       </c>
       <c r="L71" t="n">
         <v>5.75</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>4.89</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="H72" t="n">
-        <v>2409.7</v>
+        <v>2305.2</v>
       </c>
       <c r="I72" t="n">
         <v>2312.308713521773</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K72" t="n">
-        <v>1.07</v>
+        <v>-3.31</v>
       </c>
       <c r="L72" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="M72" t="n">
         <v>0.49</v>
       </c>
       <c r="N72" t="n">
-        <v>2.16</v>
+        <v>4.34</v>
       </c>
       <c r="O72" t="n">
         <v>1.54</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.04</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H73" t="n">
-        <v>2139.1</v>
+        <v>2240.8</v>
       </c>
       <c r="I73" t="n">
         <v>2205.98197341033</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K73" t="n">
-        <v>7.21</v>
+        <v>2.79</v>
       </c>
       <c r="L73" t="n">
         <v>4.11</v>
@@ -4602,7 +5477,7 @@
         <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>2.39</v>
+        <v>4.75</v>
       </c>
       <c r="O73" t="n">
         <v>-4.34</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,25 +5525,25 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H74" t="n">
-        <v>2198.4</v>
+        <v>2153.5</v>
       </c>
       <c r="I74" t="n">
         <v>2176.964208925455</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.89</v>
+        <v>-3.9</v>
       </c>
       <c r="L74" t="n">
-        <v>4.81</v>
+        <v>5.48</v>
       </c>
       <c r="M74" t="n">
-        <v>1.38</v>
+        <v>2.95</v>
       </c>
       <c r="N74" t="n">
         <v>2.74</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>105</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.5</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105.4</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="11">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.74</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.95</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.67</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.9</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.92</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.83</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.94</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="25">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="27">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
